--- a/benchmark_tools/Tang_2_Hybrid_Context/Checklist_Test_Tang_2_Handover.xlsx
+++ b/benchmark_tools/Tang_2_Hybrid_Context/Checklist_Test_Tang_2_Handover.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -641,6 +641,525 @@
       </c>
       <c r="H6" s="4" t="inlineStr"/>
     </row>
+    <row r="7" ht="133.5" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_03</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>CFG cho chuoi if / else-if / else va cac diem return som</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>public String classify(int score) {
+    if (score &gt;= 90) {
+        return "A";
+    } else if (score &gt;= 70) {
+        return "B";
+    } else {
+        return "C";
+    }
+}</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=9, V(G)=3 -&gt; ROUTE_HYBRID</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>graph TD
+  A[Start] --&gt; B{score &gt;= 90?}
+  B -- Yes --&gt; C[Return A]
+  B -- No --&gt; D{score &gt;= 70?}
+  D -- Yes --&gt; E[Return B]
+  D -- No --&gt; F[Return C]</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>if (score &gt;= 90) {
+if (score &gt;= 70) {</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n"/>
+    </row>
+    <row r="8" ht="187.5" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_04</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Vong lap for co continue va break - kiem tra canh quay lui va canh thoat vong lap</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>public int sumPositive(List&lt;Integer&gt; nums) {
+    int total = 0;
+    for (int i = 0; i &lt; nums.size(); i++) {
+        if (nums.get(i) &lt; 0) {
+            continue;
+        }
+        if (total &gt; LIMIT) {
+            break;
+        }
+        total += nums.get(i);
+    }
+    return total;
+}</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=12, V(G)=4 -&gt; ROUTE_HYBRID</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>graph TD
+  A[Start] --&gt; B[Set total = 0]
+  B --&gt; C[Init int i = 0]
+  C --&gt; D{Loop while i &lt; nums.size?}
+  D -- Yes --&gt; E{nums.get i &lt; 0?}
+  E -- Yes --&gt; F[Next i++]
+  E -- No --&gt; G{total &gt; LIMIT?}
+  G -- No --&gt; H[Update total]
+  H --&gt; F
+  F --&gt; D
+  D -- No --&gt; I[Return total]</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>for (int i = 0; i &lt; nums.size(); i++) {
+if (nums.get(i) &lt; 0) {
+if (total &gt; LIMIT) {</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="160.5" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_05</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Khoi try / catch / finally - canh exception va lenh throw ben trong catch</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>public void charge(Order order) {
+    try {
+        gateway.authorize(order.getId());
+        repository.save(order);
+    } catch (TimeoutException e) {
+        logger.error("timeout", e);
+        throw new PaymentException(e);
+    } finally {
+        lockManager.release(order.getId());
+    }
+}</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=10, V(G)=2 -&gt; ROUTE_HYBRID</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>graph TD
+  A[Start] --&gt; B[Try]
+  B --&gt; C[Authorize gateway]
+  C --&gt; D[Save order]
+  B -- exception --&gt; E[Catch Timeout]
+  E --&gt; F[Error logger]
+  F --&gt; G[Throw Payment]
+  D --&gt; H[Finally]
+  H --&gt; I[Release lockManager]</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>catch (TimeoutException e)
+throw new PaymentException(e);</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n"/>
+    </row>
+    <row r="10" ht="147" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_06</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Switch nhieu nhanh co default - moi case phai la mot canh rieng</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>public double fee(String type) {
+    switch (type) {
+        case "VIP":
+            return 0;
+        case "NORMAL":
+            return 10;
+        default:
+            return 20;
+    }
+}</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=9, V(G)=3 -&gt; ROUTE_HYBRID</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>graph TD
+  A[Start] --&gt; B{Switch on type?}
+  B -- case VIP --&gt; C[Return 0]
+  B -- case NORMAL --&gt; D[Return 10]
+  B -- default --&gt; E[Return 20]</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>switch (type) {</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="174" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_07</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Ma nguon C# async/await - nhan dien async marker va khoi using</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>csharp</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>public async Task&lt;Result&gt; SaveAsync(Request request, CancellationToken ct)
+{
+    if (request is null)
+    {
+        throw new ArgumentNullException(nameof(request));
+    }
+    using (var scope = _factory.CreateScope())
+    {
+        var saved = await _repository.SaveAsync(request, ct);
+        return Result.Ok(saved);
+    }
+}</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=11, V(G)=2 -&gt; ROUTE_HYBRID</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>graph TD
+  A[Start] --&gt; B{request is null?}
+  B -- Yes --&gt; C[Throw ArgumentNull]
+  B -- No --&gt; D[using var scope = _factory.CreateScope]
+  D --&gt; E[Set saved = await _repository.SaveAsync]
+  E --&gt; F[Return Result.Ok saved]</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>throw new ArgumentNullException(nameof(request));
+var saved = await _repository.SaveAsync(request, ct);</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n"/>
+    </row>
+    <row r="12" ht="174" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_08</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Vong lap long nhau while + do-while, co break thoat vong ngoai</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>public void retrySync(Job job) {
+    int attempt = 0;
+    while (attempt &lt; 3) {
+        do {
+            queue.push(job);
+            attempt++;
+        } while (queue.isFull());
+        if (job.isDone()) {
+            break;
+        }
+    }
+}</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=11, V(G)=4 -&gt; ROUTE_HYBRID</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>graph TD
+  A[Start] --&gt; B[Set attempt = 0]
+  B --&gt; C{Loop while attempt &lt; 3?}
+  C -- Yes --&gt; D[Do]
+  D --&gt; E[Push job queue]
+  E --&gt; F[Increase attempt]
+  F --&gt; G{Repeat while queue.isFull?}
+  G -- Yes --&gt; D
+  G -- No --&gt; H{job.isDone?}
+  H -- No --&gt; C
+  C -- No --&gt; I[End]</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>while (attempt &lt; 3) {
+if (job.isDone()) {</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n"/>
+    </row>
+    <row r="13" ht="201" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_09</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Class co nhieu ham - moi ham mot do thi con (subgraph) rieng</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>public class OrderValidator {
+    public boolean isValid(Order order) {
+        if (order == null) {
+            return false;
+        }
+        return order.getTotal() &gt; 0;
+    }
+    public void assertValid(Order order) {
+        if (!isValid(order)) {
+            throw new ValidationException("invalid order");
+        }
+    }
+}</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=12, V(G)=4 -&gt; ROUTE_HYBRID</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>graph TD
+  subgraph isValid
+  A[Start] --&gt; B{order == null?}
+  B -- Yes --&gt; C[Return false]
+  B -- No --&gt; D[Return order.getTotal &gt; 0]
+  end
+  subgraph assertValid
+  E[Start] --&gt; F{!isValid?}
+  F -- Yes --&gt; G[Throw Validation]
+  end</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>if (order == null) {
+if (!isValid(order)) {
+throw new ValidationException("invalid order");</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n"/>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_10</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Ma nguon loi cu phap (thieu dau ngoac) - Tang 2 phai tra HTTP 200, khong duoc treo hay 500</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>public void broken(Order order) {
+    if (order == null {
+        save(order);
+}</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=4, V(G)=2 -&gt; ROUTE_HYBRID (AST hasError)</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="4" t="n"/>
+    </row>
+    <row r="15" ht="106.5" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_11</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Comment va chuoi chua ky tu gay nhieu ( ; { } if ) - khong duoc tinh thanh nhanh re</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>public void log(User u) {
+    // if (u == null) throw new Fake();
+    String msg = "user; {id} =&gt; " + u.getId();
+    if (u.isActive()) {
+        auditLogger.info(msg);
+    }
+}</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=6, V(G)=2 -&gt; ROUTE_HYBRID</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>graph TD
+  A[Start] --&gt; B[Set msg]
+  B --&gt; C{u.isActive?}
+  C -- Yes --&gt; D[Info auditLogger]
+  C -- No --&gt; E[End]</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>if (u.isActive()) {</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n"/>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>TC_H_12</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Ham tuyen tinh khong nhanh re (dang le di ROUTE_RAW_CODE) - Tang 2 van sinh CFG hop le</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>public String greet(User u) {
+    String name = u.getName();
+    return "Hello " + name;
+}</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>SLOC=4, V(G)=1 -&gt; ROUTE_RAW_CODE</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>graph TD
+  A[Start] --&gt; B[Set name = u.getName]
+  B --&gt; C[Return Hello name]
+  C --&gt; D[End]</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr"/>
+      <c r="H16" s="4" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
